--- a/output/pdf_financials_xlsx/A.H.xlsx
+++ b/output/pdf_financials_xlsx/A.H.xlsx
@@ -1504,16 +1504,16 @@
         <v>2.669868</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>4.73706</v>
+        <v>-4.73706</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>3.633062</v>
+        <v>-3.633062</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.495534</v>
+        <v>-0.495534</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.141557</v>
+        <v>-0.141557</v>
       </c>
       <c r="I16" s="1" t="inlineStr">
         <is>
@@ -1541,13 +1541,13 @@
         </is>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.096396</v>
+        <v>-0.096396</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.10973</v>
+        <v>-0.10973</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.165801</v>
+        <v>-0.165801</v>
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-9.658758000000001</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.009586000000000001</v>
+        <v>-3.96269</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2.453003</v>
+        <v>-7.792739</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1843,25 +1843,25 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>4.829379</v>
+        <v>-4.829379</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.976552</v>
+        <v>-1.976552</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>5.122871</v>
+        <v>-5.122871</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>4.73706</v>
+        <v>-4.73706</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.633062</v>
+        <v>-3.633062</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.495534</v>
+        <v>-0.495534</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.141557</v>
+        <v>-0.141557</v>
       </c>
       <c r="I20" s="1" t="inlineStr">
         <is>
@@ -1889,13 +1889,13 @@
         </is>
       </c>
       <c r="N20" s="3" t="n">
-        <v>0.096396</v>
+        <v>-0.096396</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.10973</v>
+        <v>-0.10973</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.165801</v>
+        <v>-0.165801</v>
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
@@ -2074,25 +2074,25 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>4.829379</v>
+        <v>-4.829379</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.976552</v>
+        <v>-1.976552</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>5.122871</v>
+        <v>-5.122871</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>4.73706</v>
+        <v>-4.73706</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.633062</v>
+        <v>-3.633062</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.495534</v>
+        <v>-0.495534</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.141557</v>
+        <v>-0.141557</v>
       </c>
       <c r="I23" s="1" t="inlineStr">
         <is>
@@ -2114,13 +2114,13 @@
         <v>-0.242498</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>0.096396</v>
+        <v>-0.096396</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.10973</v>
+        <v>-0.10973</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.165801</v>
+        <v>-0.165801</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>0.008355</v>
@@ -2305,25 +2305,25 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>21.951723</v>
+        <v>-21.951723</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>49.4138</v>
+        <v>-49.4138</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>85.38118299999999</v>
+        <v>-85.38118299999999</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>157.902</v>
+        <v>-157.902</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>14.532248</v>
+        <v>-14.532248</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1.708738</v>
+        <v>-1.708738</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>1.769462</v>
+        <v>-1.769462</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -2397,16 +2397,16 @@
         <v>2.674766</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>4.752605</v>
+        <v>-4.721515</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.633796</v>
+        <v>-3.632328</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.495606</v>
+        <v>-0.495462</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.141557</v>
+        <v>-0.141557</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -2434,13 +2434,13 @@
         </is>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.111468</v>
+        <v>-0.08132399999999999</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.117202</v>
+        <v>-0.102258</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.230819</v>
+        <v>-0.100783</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2551,16 +2551,16 @@
         <v>2.674766</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>4.752605</v>
+        <v>-4.721515</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.633796</v>
+        <v>-3.632328</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.495606</v>
+        <v>-0.495462</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.141557</v>
+        <v>-0.141557</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.111468</v>
+        <v>-0.08132399999999999</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.117202</v>
+        <v>-0.102258</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.230819</v>
+        <v>-0.100783</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2716,25 +2716,25 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.4826452139780821</v>
+        <v>199.5173547860219</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>91.87731378480134</v>
+        <v>291.8773137848013</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="1" t="inlineStr">
         <is>
@@ -2762,13 +2762,13 @@
         </is>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
@@ -6596,43 +6596,43 @@
         <v>2.1334</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>2.147818</v>
+        <v>2.373983</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>2.147944</v>
+        <v>2.724088</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.682872</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>4.002029</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>4.001522</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.929489</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.929483</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.065968</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>2.85223</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>2.85223</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>2.85223</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>2.85223</v>
       </c>
       <c r="S92" s="3" t="n">
-        <v>0</v>
+        <v>2.85223</v>
       </c>
     </row>
     <row r="93">
@@ -10508,7 +10508,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>
@@ -13086,7 +13090,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -15480,7 +15488,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -17678,7 +17690,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -19266,7 +19282,11 @@
           <t>Reserves (note 6)</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -22832,7 +22852,11 @@
           <t>Reserves (note 7)</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -45898,13 +45922,13 @@
         </is>
       </c>
       <c r="Q350" s="5" t="n">
-        <v>0.096396</v>
+        <v>-0.096396</v>
       </c>
       <c r="R350" s="5" t="n">
-        <v>0.10973</v>
+        <v>-0.10973</v>
       </c>
       <c r="S350" s="5" t="n">
-        <v>0.165801</v>
+        <v>-0.165801</v>
       </c>
       <c r="T350" t="inlineStr">
         <is>
@@ -48277,10 +48301,10 @@
         </is>
       </c>
       <c r="J373" s="5" t="n">
-        <v>0.495534</v>
+        <v>-0.495534</v>
       </c>
       <c r="K373" s="5" t="n">
-        <v>0.141557</v>
+        <v>-0.141557</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
@@ -49836,16 +49860,16 @@
         </is>
       </c>
       <c r="G388" s="5" t="n">
-        <v>5.122871</v>
+        <v>-5.122871</v>
       </c>
       <c r="H388" s="5" t="n">
-        <v>4.73706</v>
+        <v>-4.73706</v>
       </c>
       <c r="I388" s="5" t="n">
-        <v>3.633062</v>
+        <v>-3.633062</v>
       </c>
       <c r="J388" s="5" t="n">
-        <v>0.495534</v>
+        <v>-0.495534</v>
       </c>
       <c r="K388" t="inlineStr">
         <is>
@@ -52263,10 +52287,10 @@
         </is>
       </c>
       <c r="F411" s="5" t="n">
-        <v>1.976552</v>
+        <v>-1.976552</v>
       </c>
       <c r="G411" s="5" t="n">
-        <v>2.669868</v>
+        <v>-2.669868</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
@@ -54704,10 +54728,10 @@
         </is>
       </c>
       <c r="E434" s="5" t="n">
-        <v>4.829379</v>
+        <v>-4.829379</v>
       </c>
       <c r="F434" s="5" t="n">
-        <v>1.976552</v>
+        <v>-1.976552</v>
       </c>
       <c r="G434" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/A.H.xlsx
+++ b/output/pdf_financials_xlsx/A.H.xlsx
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.041611</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000334</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>-0.004898</v>
@@ -2388,10 +2388,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>4.829379</v>
+        <v>4.87099</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.986138</v>
+        <v>1.986472</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>2.674766</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>4.829379</v>
+        <v>4.87099</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.986138</v>
+        <v>1.986472</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>2.674766</v>
@@ -2906,10 +2906,10 @@
         <v>5.331379</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.890642</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.008240000000000001</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.007309</v>
@@ -3028,10 +3028,10 @@
         <v>5.331379</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.890642</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.008240000000000001</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.007309</v>
@@ -3760,10 +3760,10 @@
         <v>0.017987</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.906606</v>
+        <v>0.015964</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.019608</v>
+        <v>0.011368</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -24510,7 +24510,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -51850,7 +51850,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -54188,7 +54188,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E429" s="5" t="n">
